--- a/access_control_forms/014_jobsite_security_surveillance_log--access_control_forms.xlsx
+++ b/access_control_forms/014_jobsite_security_surveillance_log--access_control_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'no_incident'}</t>
+          <t>no_incident</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'No Incident'}</t>
+          <t>No Incident</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'incident_reported'}</t>
+          <t>incident_reported</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Incident Reported'}</t>
+          <t>Incident Reported</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'incident_under_investigation'}</t>
+          <t>incident_under_investigation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Incident Under Investigation'}</t>
+          <t>Incident Under Investigation</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'incident_closed'}</t>
+          <t>incident_closed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Incident Closed'}</t>
+          <t>Incident Closed</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'police_vehicle'}</t>
+          <t>police_vehicle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Police Vehicle'}</t>
+          <t>Police Vehicle</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'fire_truck'}</t>
+          <t>fire_truck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Fire Truck'}</t>
+          <t>Fire Truck</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'ambulance'}</t>
+          <t>ambulance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Ambulance'}</t>
+          <t>Ambulance</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'officer_a'}</t>
+          <t>officer_a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Officer A'}</t>
+          <t>Officer A</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'officer_b'}</t>
+          <t>officer_b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Officer B'}</t>
+          <t>Officer B</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'not_resolved'}</t>
+          <t>not_resolved</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Not Resolved'}</t>
+          <t>Not Resolved</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
